--- a/workers.xlsx
+++ b/workers.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>first_name</t>
   </si>
@@ -78,6 +78,15 @@
   </si>
   <si>
     <t>alex@mail.ru</t>
+  </si>
+  <si>
+    <t>Peter2</t>
+  </si>
+  <si>
+    <t>Adams2</t>
+  </si>
+  <si>
+    <t>nonname@miss.ru</t>
   </si>
 </sst>
 </file>
@@ -426,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.77734375" customWidth="1"/>
@@ -502,12 +511,36 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" display="mailto:peter@test.ru"/>
     <hyperlink ref="C3" r:id="rId2" display="mailto:jane@example.com"/>
     <hyperlink ref="C2" r:id="rId3" display="mailto:john@example.com"/>
     <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5" display="mailto:peter@test.ru"/>
+    <hyperlink ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
